--- a/20240304_binary_files/output/20240304_binary_files_site_pairs.xlsx
+++ b/20240304_binary_files/output/20240304_binary_files_site_pairs.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rh-Sb" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Th-Os" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Os-Os" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Nd-Si" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Si-Si" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Sb" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Os-Os" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Th-Os" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si-Si" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Si" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -475,9 +475,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.584</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -490,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,13 +544,38 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.198</v>
+        <v>2.728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.728</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -536,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,13 +615,38 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.728</v>
+        <v>3.198</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.198</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -582,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,43 +686,38 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.08</v>
+        <v>2.755</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Nd5Si3.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.082</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nd5Si3.cif</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.215</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+        <v>2.755</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -658,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,13 +757,70 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.755</v>
+        <v>3.08</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nd5Si3.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.082</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nd5Si3.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.215</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.126</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
